--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,2184 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129728461</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>492660</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7134794</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129726712</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78088</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>492711</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7134828</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129726715</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>492662</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7134858</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129726713</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>492699</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7134833</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129728467</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>492724</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7134833</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129728468</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>492661</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7134854</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129726714</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>492687</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7134838</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129728465</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>492698</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7134791</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129728463</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>492678</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7134751</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129728460</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>492616</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7134774</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129728464</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>492609</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7134774</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129726710</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>492730</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7134706</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129728458</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>492653</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7134804</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i en granstubbe.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129728466</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>492720</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7134826</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129728462</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>492561</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7134839</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129726711</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>492719</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7134787</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129726709</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57839</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>492676</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7134712</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129728459</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Strockbergen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>492676</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7134777</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor inom ca 0,5 m2 yta. Finns troligen fler plantor på och omkring fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1143,65 +1143,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129728461</v>
+        <v>129726712</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>78089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492660</v>
+        <v>492711</v>
       </c>
       <c r="R6" t="n">
-        <v>7134794</v>
+        <v>7134828</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,14 +1211,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,69 +1232,83 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726712</v>
+        <v>129728461</v>
       </c>
       <c r="B7" t="n">
-        <v>78088</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492711</v>
+        <v>492660</v>
       </c>
       <c r="R7" t="n">
-        <v>7134828</v>
+        <v>7134794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,19 +1338,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,18 +1354,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
         <v>129726715</v>
       </c>
       <c r="B8" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>129726713</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>129728467</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129728468</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129726714</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>129728465</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129728463</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129728460</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>129728464</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129726710</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>129728458</v>
       </c>
       <c r="B18" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>129728466</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>129728462</v>
       </c>
       <c r="B20" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>129726711</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>129726709</v>
       </c>
       <c r="B22" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129728459</v>
       </c>
       <c r="B23" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1143,45 +1143,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726712</v>
+        <v>129728461</v>
       </c>
       <c r="B6" t="n">
-        <v>78089</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492711</v>
+        <v>492660</v>
       </c>
       <c r="R6" t="n">
-        <v>7134828</v>
+        <v>7134794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,19 +1231,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,83 +1247,69 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728461</v>
+        <v>129726712</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>78094</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492660</v>
+        <v>492711</v>
       </c>
       <c r="R7" t="n">
-        <v>7134794</v>
+        <v>7134828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,14 +1339,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,24 +1360,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
         <v>129726715</v>
       </c>
       <c r="B8" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>129726713</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>129728467</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129728468</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129726714</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>129728465</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129728463</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129728460</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>129728464</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129726710</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>129728466</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>129728462</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>129726711</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129728459</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1143,65 +1143,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129728461</v>
+        <v>129726712</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>78094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492660</v>
+        <v>492711</v>
       </c>
       <c r="R6" t="n">
-        <v>7134794</v>
+        <v>7134828</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,14 +1211,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,69 +1232,83 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726712</v>
+        <v>129728461</v>
       </c>
       <c r="B7" t="n">
-        <v>78094</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492711</v>
+        <v>492660</v>
       </c>
       <c r="R7" t="n">
-        <v>7134828</v>
+        <v>7134794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,19 +1338,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,18 +1354,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129728464</v>
+        <v>129728458</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,37 +2357,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492609</v>
+        <v>492653</v>
       </c>
       <c r="R16" t="n">
-        <v>7134774</v>
+        <v>7134804</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2422,13 +2431,17 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i en granstubbe.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2449,12 +2462,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2472,7 +2485,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726710</v>
+        <v>129728464</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2501,16 +2514,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492730</v>
+        <v>492609</v>
       </c>
       <c r="R17" t="n">
-        <v>7134706</v>
+        <v>7134774</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,49 +2556,65 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129728458</v>
+        <v>129726710</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,46 +2622,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492653</v>
+        <v>492730</v>
       </c>
       <c r="R18" t="n">
-        <v>7134804</v>
+        <v>7134706</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2659,14 +2679,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i en granstubbe.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2677,41 +2702,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -2346,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129728458</v>
+        <v>129728464</v>
       </c>
       <c r="B16" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,46 +2357,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492653</v>
+        <v>492609</v>
       </c>
       <c r="R16" t="n">
-        <v>7134804</v>
+        <v>7134774</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2431,17 +2422,13 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2462,12 +2449,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2485,7 +2472,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129728464</v>
+        <v>129726710</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2514,19 +2501,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492609</v>
+        <v>492730</v>
       </c>
       <c r="R17" t="n">
-        <v>7134774</v>
+        <v>7134706</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2556,65 +2540,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726710</v>
+        <v>129728458</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,34 +2590,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492730</v>
+        <v>492653</v>
       </c>
       <c r="R18" t="n">
-        <v>7134706</v>
+        <v>7134804</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,19 +2659,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:31</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i en granstubbe.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2702,16 +2677,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2975,45 +2975,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726711</v>
+        <v>129726709</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>57840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492719</v>
+        <v>492676</v>
       </c>
       <c r="R21" t="n">
-        <v>7134787</v>
+        <v>7134712</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3045,7 +3049,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3055,7 +3059,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3082,49 +3086,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726709</v>
+        <v>129726711</v>
       </c>
       <c r="B22" t="n">
-        <v>57840</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492676</v>
+        <v>492719</v>
       </c>
       <c r="R22" t="n">
-        <v>7134712</v>
+        <v>7134787</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1143,45 +1143,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726712</v>
+        <v>129728461</v>
       </c>
       <c r="B6" t="n">
-        <v>78094</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492711</v>
+        <v>492660</v>
       </c>
       <c r="R6" t="n">
-        <v>7134828</v>
+        <v>7134794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,19 +1231,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,83 +1247,69 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728461</v>
+        <v>129726712</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>78094</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492660</v>
+        <v>492711</v>
       </c>
       <c r="R7" t="n">
-        <v>7134794</v>
+        <v>7134828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,14 +1339,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,24 +1360,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129726714</v>
+        <v>129728465</v>
       </c>
       <c r="B12" t="n">
         <v>79081</v>
@@ -1883,16 +1883,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492687</v>
+        <v>492698</v>
       </c>
       <c r="R12" t="n">
-        <v>7134838</v>
+        <v>7134791</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,19 +1925,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:22</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,25 +1941,51 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129728465</v>
+        <v>129726714</v>
       </c>
       <c r="B13" t="n">
         <v>79081</v>
@@ -1990,19 +2014,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492698</v>
+        <v>492687</v>
       </c>
       <c r="R13" t="n">
-        <v>7134791</v>
+        <v>7134838</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,14 +2053,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,44 +2074,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2975,49 +2975,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726709</v>
+        <v>129726711</v>
       </c>
       <c r="B21" t="n">
-        <v>57840</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492676</v>
+        <v>492719</v>
       </c>
       <c r="R21" t="n">
-        <v>7134712</v>
+        <v>7134787</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3049,7 +3045,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3059,7 +3055,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3086,45 +3082,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726711</v>
+        <v>129726709</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>57840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492719</v>
+        <v>492676</v>
       </c>
       <c r="R22" t="n">
-        <v>7134787</v>
+        <v>7134712</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129728461</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129726715</v>
       </c>
       <c r="B8" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129728460</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129728459</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1143,65 +1143,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129728461</v>
+        <v>129726712</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>78094</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492660</v>
+        <v>492711</v>
       </c>
       <c r="R6" t="n">
-        <v>7134794</v>
+        <v>7134828</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,14 +1211,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,69 +1232,83 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129726712</v>
+        <v>129728461</v>
       </c>
       <c r="B7" t="n">
-        <v>78094</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492711</v>
+        <v>492660</v>
       </c>
       <c r="R7" t="n">
-        <v>7134828</v>
+        <v>7134794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,19 +1338,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,18 +1354,24 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
         <v>129726715</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129728465</v>
+        <v>129726714</v>
       </c>
       <c r="B12" t="n">
         <v>79081</v>
@@ -1883,19 +1883,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492698</v>
+        <v>492687</v>
       </c>
       <c r="R12" t="n">
-        <v>7134791</v>
+        <v>7134838</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1925,14 +1922,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,51 +1943,25 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129726714</v>
+        <v>129728465</v>
       </c>
       <c r="B13" t="n">
         <v>79081</v>
@@ -2014,16 +1990,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492687</v>
+        <v>492698</v>
       </c>
       <c r="R13" t="n">
-        <v>7134838</v>
+        <v>7134791</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,19 +2032,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:22</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,18 +2048,44 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2221,7 +2221,7 @@
         <v>129728460</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129728459</v>
       </c>
       <c r="B23" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -2975,45 +2975,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726711</v>
+        <v>129726709</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>57840</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492719</v>
+        <v>492676</v>
       </c>
       <c r="R21" t="n">
-        <v>7134787</v>
+        <v>7134712</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3045,7 +3049,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3055,7 +3059,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3082,49 +3086,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726709</v>
+        <v>129726711</v>
       </c>
       <c r="B22" t="n">
-        <v>57840</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492676</v>
+        <v>492719</v>
       </c>
       <c r="R22" t="n">
-        <v>7134712</v>
+        <v>7134787</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -2346,7 +2346,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129728464</v>
+        <v>129726710</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2375,19 +2375,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492609</v>
+        <v>492730</v>
       </c>
       <c r="R16" t="n">
-        <v>7134774</v>
+        <v>7134706</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,62 +2414,46 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726710</v>
+        <v>129728464</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2501,16 +2482,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492730</v>
+        <v>492609</v>
       </c>
       <c r="R17" t="n">
-        <v>7134706</v>
+        <v>7134774</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,39 +2524,55 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>129728461</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129728460</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129726710</v>
+        <v>129728464</v>
       </c>
       <c r="B16" t="n">
         <v>79081</v>
@@ -2375,16 +2375,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492730</v>
+        <v>492609</v>
       </c>
       <c r="R16" t="n">
-        <v>7134706</v>
+        <v>7134774</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,46 +2417,62 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129728464</v>
+        <v>129726710</v>
       </c>
       <c r="B17" t="n">
         <v>79081</v>
@@ -2482,19 +2501,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492609</v>
+        <v>492730</v>
       </c>
       <c r="R17" t="n">
-        <v>7134774</v>
+        <v>7134706</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2524,55 +2540,39 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3196,7 +3196,7 @@
         <v>129728459</v>
       </c>
       <c r="B23" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -2975,49 +2975,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726709</v>
+        <v>129726711</v>
       </c>
       <c r="B21" t="n">
-        <v>57840</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492676</v>
+        <v>492719</v>
       </c>
       <c r="R21" t="n">
-        <v>7134712</v>
+        <v>7134787</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3049,7 +3045,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3059,7 +3055,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3086,45 +3082,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726711</v>
+        <v>129726709</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>57840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492719</v>
+        <v>492676</v>
       </c>
       <c r="R22" t="n">
-        <v>7134787</v>
+        <v>7134712</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1143,45 +1143,65 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129726712</v>
+        <v>129728461</v>
       </c>
       <c r="B6" t="n">
-        <v>78094</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492711</v>
+        <v>492660</v>
       </c>
       <c r="R6" t="n">
-        <v>7134828</v>
+        <v>7134794</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,19 +1231,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:25</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,83 +1247,69 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129728461</v>
+        <v>129726712</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>78097</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492660</v>
+        <v>492711</v>
       </c>
       <c r="R7" t="n">
-        <v>7134794</v>
+        <v>7134828</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,14 +1339,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 12 plantor inom ca 0,5 m2 yta ca 5 meter sydväst om en stubbe med hackspår efter spillkråka.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,24 +1360,18 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
         <v>129726715</v>
       </c>
       <c r="B8" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>129726713</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>129728467</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129728468</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129726714</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>129728465</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129728463</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129728460</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>129728464</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129726710</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>129728458</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>129728466</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>129728462</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2975,45 +2975,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726711</v>
+        <v>129726709</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>57841</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492719</v>
+        <v>492676</v>
       </c>
       <c r="R21" t="n">
-        <v>7134787</v>
+        <v>7134712</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3045,7 +3049,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3055,7 +3059,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3082,49 +3086,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726709</v>
+        <v>129726711</v>
       </c>
       <c r="B22" t="n">
-        <v>57840</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492676</v>
+        <v>492719</v>
       </c>
       <c r="R22" t="n">
-        <v>7134712</v>
+        <v>7134787</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3196,7 +3196,7 @@
         <v>129728459</v>
       </c>
       <c r="B23" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -2975,49 +2975,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129726709</v>
+        <v>129726711</v>
       </c>
       <c r="B21" t="n">
-        <v>57841</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492676</v>
+        <v>492719</v>
       </c>
       <c r="R21" t="n">
-        <v>7134712</v>
+        <v>7134787</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3049,7 +3045,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3059,7 +3055,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3086,45 +3082,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129726711</v>
+        <v>129726709</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>57841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492719</v>
+        <v>492676</v>
       </c>
       <c r="R22" t="n">
-        <v>7134787</v>
+        <v>7134712</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129728461</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129726712</v>
       </c>
       <c r="B7" t="n">
-        <v>78097</v>
+        <v>78100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129726715</v>
       </c>
       <c r="B8" t="n">
-        <v>91598</v>
+        <v>91601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>129726713</v>
       </c>
       <c r="B9" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>129728467</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129728468</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129726714</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>129728465</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129728463</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129728460</v>
       </c>
       <c r="B15" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129728464</v>
+        <v>129728458</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,37 +2357,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492609</v>
+        <v>492653</v>
       </c>
       <c r="R16" t="n">
-        <v>7134774</v>
+        <v>7134804</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2422,13 +2431,17 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i en granstubbe.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2449,12 +2462,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2472,10 +2485,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129726710</v>
+        <v>129728464</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,16 +2514,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492730</v>
+        <v>492609</v>
       </c>
       <c r="R17" t="n">
-        <v>7134706</v>
+        <v>7134774</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,49 +2556,65 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129728458</v>
+        <v>129726710</v>
       </c>
       <c r="B18" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,46 +2622,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492653</v>
+        <v>492730</v>
       </c>
       <c r="R18" t="n">
-        <v>7134804</v>
+        <v>7134706</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2659,14 +2679,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i en granstubbe.</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2677,41 +2702,16 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2721,7 +2721,7 @@
         <v>129728466</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>129728462</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>129726711</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>129726709</v>
       </c>
       <c r="B22" t="n">
-        <v>57841</v>
+        <v>57844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129728459</v>
       </c>
       <c r="B23" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -2346,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129728458</v>
+        <v>129728464</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,46 +2357,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492653</v>
+        <v>492609</v>
       </c>
       <c r="R16" t="n">
-        <v>7134804</v>
+        <v>7134774</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2431,17 +2422,13 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2462,12 +2449,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2485,7 +2472,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129728464</v>
+        <v>129726710</v>
       </c>
       <c r="B17" t="n">
         <v>79087</v>
@@ -2514,19 +2501,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492609</v>
+        <v>492730</v>
       </c>
       <c r="R17" t="n">
-        <v>7134774</v>
+        <v>7134706</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2556,65 +2540,49 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129726710</v>
+        <v>129728458</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,34 +2590,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492730</v>
+        <v>492653</v>
       </c>
       <c r="R18" t="n">
-        <v>7134706</v>
+        <v>7134804</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,19 +2659,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:31</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i en granstubbe.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2702,16 +2677,41 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129728461</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129726715</v>
       </c>
       <c r="B8" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>129726713</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>129728467</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129728468</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>129726714</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>129728465</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>129728463</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129728460</v>
       </c>
       <c r="B15" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
         <v>129728464</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129726710</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>129728466</v>
       </c>
       <c r="B19" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>129728462</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>129726711</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129728459</v>
       </c>
       <c r="B23" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 56137-2025 artfynd.xlsx
+++ b/artfynd/A 56137-2025 artfynd.xlsx
@@ -1146,7 +1146,7 @@
         <v>129728461</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129726712</v>
       </c>
       <c r="B7" t="n">
-        <v>78100</v>
+        <v>78101</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>129726715</v>
       </c>
       <c r="B8" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>129726713</v>
       </c>
       <c r="B9" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>129728467</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>129728468</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129726714</v>
+        <v>129728465</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,16 +1883,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492687</v>
+        <v>492698</v>
       </c>
       <c r="R12" t="n">
-        <v>7134838</v>
+        <v>7134791</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1922,19 +1925,14 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:22</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,28 +1941,54 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129728465</v>
+        <v>129726714</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1990,19 +2014,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492698</v>
+        <v>492687</v>
       </c>
       <c r="R13" t="n">
-        <v>7134791</v>
+        <v>7134838</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,14 +2053,19 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,44 +2074,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2095,7 +2095,7 @@
         <v>129728463</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>129728460</v>
       </c>
       <c r="B15" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129728464</v>
+        <v>129728458</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2357,37 +2357,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492609</v>
+        <v>492653</v>
       </c>
       <c r="R16" t="n">
-        <v>7134774</v>
+        <v>7134804</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2422,13 +2431,17 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre rejäla hackspår i en granstubbe.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2449,12 +2462,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2475,7 +2488,7 @@
         <v>129726710</v>
       </c>
       <c r="B17" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2579,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129728458</v>
+        <v>129728464</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,46 +2603,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Strockbergen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492653</v>
+        <v>492609</v>
       </c>
       <c r="R18" t="n">
-        <v>7134804</v>
+        <v>7134774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2664,17 +2668,13 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre rejäla hackspår i en granstubbe.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2695,12 +2695,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129728466</v>
+        <v>129728462</v>
       </c>
       <c r="B19" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492720</v>
+        <v>492561</v>
       </c>
       <c r="R19" t="n">
-        <v>7134826</v>
+        <v>7134839</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2794,11 +2794,6 @@
           <t>2025-11-16</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2811,7 +2806,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2849,10 +2844,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129728462</v>
+        <v>129728466</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,10 +2882,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492561</v>
+        <v>492720</v>
       </c>
       <c r="R20" t="n">
-        <v>7134839</v>
+        <v>7134826</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2925,6 +2920,11 @@
           <t>2025-11-16</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -2978,7 +2978,7 @@
         <v>129726711</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>129728459</v>
       </c>
       <c r="B23" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
